--- a/article-content/reports/NIAT_Insider_completed_articles.xlsx
+++ b/article-content/reports/NIAT_Insider_completed_articles.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Completed articles'!$A$1:$E$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Completed articles'!$A$1:$E$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
         <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +121,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -484,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2317,7 +2325,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Chaitanya Deemed to be University  (11 articles)</t>
+          <t>Chaitanya Deemed to be University  (12 articles)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n"/>
@@ -2685,55 +2693,84 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
+          <t>https://www.niatinsider.com/niat-chaitanya-university/article/ai-trends-2026-openai-gpt-amazon-google-updates</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-chaitanya-university/articles
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Removed from the site: a news roundup with unsourced claims is not a student experience article. Write about your own experience at the campus and resubmit.
+Only 252 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Chaitanya Deemed to be University</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
           <t>https://www.niatinsider.com/niat-chaitanya-university/article/qr-code-sports-feedback-chaitanya-university-hyderabad</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-chaitanya-university/article/qr-codes-student-queries-chaitanya-hyderabad
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Merged into another article on this campus, which now includes this article's details.
 Only 247 words</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Annamacharya University  (7 articles)</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-career-growth-wins-what-students-actually-experience</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Career &amp; Wins at NIAT: What Growth Actually Looks Like" → "What Career Growth at NIAT Kadapa Actually Looks Like"
 Meta title: "Career Growth at NIAT Kadapa: What Wins Look Like"
@@ -2742,7 +2779,7 @@
 Body rewritten from the SEO report (404 → 682 words); H2 headings 0 → 8; FAQ section added</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -2752,23 +2789,23 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-kadapa-pg-hostel-food-survival-guide</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Survival at NIAT: Managing Food, Stay, and Daily Life Smartly" → "PG or Hostel at NIAT Kadapa: Managing Food, Stay and Daily Life"
 Meta title: "PG or Hostel at NIAT Kadapa? What Students Choose"
@@ -2777,7 +2814,7 @@
 Body rewritten from the SEO report (431 → 642 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 61 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -2787,23 +2824,23 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-student-clubs-real-growth-kadapa</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Clubs at NIAT: Where Students Actually Grow" → "Clubs at NIAT Kadapa: Where Students Actually Grow"
 Meta title: "Clubs at NIAT Kadapa: All Seven and What They Do"
@@ -2812,7 +2849,7 @@
 Body rewritten from the SEO report (477 → 704 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -2822,23 +2859,23 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-student-coding-leadership-journey-annamacharya</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Meta title: "From Debugging to President: A NIAT Kadapa Story"
 Meta description rewritten with the article's own specifics
@@ -2846,7 +2883,7 @@
 Body rewritten from the SEO report (308 → 462 words); H2 headings 0 → 3; FAQ section added</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was 163 characters (over 160)
@@ -2855,23 +2892,23 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-student-hangout-spots-kadapa-tea-shops</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Beyond Campus: Where NIAT Students Actually Hang Out" → "Beyond Campus: Where NIAT Kadapa Students Actually Hang Out"
 Meta title: "Where NIAT Kadapa Students Actually Hang Out"
@@ -2880,7 +2917,7 @@
 Body rewritten from the SEO report (388 → 526 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -2890,23 +2927,23 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/what-they-dont-tell-you-before-joining-niat</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "What They Don’t Tell You Before Joining NIAT" → "What They Don't Tell You Before Joining NIAT Kadapa"
 Meta title: "What Nobody Tells You Before Joining NIAT Kadapa"
@@ -2915,7 +2952,7 @@
 Body rewritten from the SEO report (492 → 736 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -2925,100 +2962,210 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Annamacharya University</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-annamacharya-university/article/niat-admission-fee-structure-reality-check</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Removed</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Unpublished (rejected) and removed from sitemap</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Removed from the site while the editorial team reviews it.
 Only 104 words</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Kapil Kavuri Hub  (1 articles)</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-    </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Kapil Kavuri Hub  (5 articles)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Kapil Kavuri Hub</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/kkh-niat/article/cafeteria-heart-of-campus-life-niat-hyderabad</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Body formatting fixed, text kept (595 → 595 words)</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Formatting fixes only: typed '--' dashes, broken link, repeated opening lines, pasted chat-app styling</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Nadimpalli Satyanarayana Raju Institute of Technology  (58 articles)</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
+          <t>Kapil Kavuri Hub</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/kkh-niat/article/college-not-just-degree-skills-development-after-12th-grade-niat-kkh</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 531 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Kavuri Hub</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/kkh-niat/article/first-year-web-development-python-dsa-mern-tech-career-start-niat-kkh</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 458 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Kavuri Hub</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/kkh-niat/article/real-playbook-making-four-years-count-btech-niat-kkh</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 8 H2 sections and 645 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Kavuri Hub</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/kkh-niat/article/onboarding-kit-the-first-step-into-campus-life-046d1326</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Unpublished and 301-redirected to https://www.niatinsider.com/kkh-niat/articles
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
+Only 310 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology  (66 articles)</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/30-days-at-niat-c72fc884</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "30 Days at NIAT" → "First 30 Days at NIAT NSRIT: Learning, Friends and Campus Life"
 Meta title: "First 30 Days at NIAT NSRIT: Campus Life"
@@ -3026,7 +3173,7 @@
 Body rewritten from the SEO report (524 → 453 words); H2 headings 1 → 6; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3035,23 +3182,23 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/30-days-at-niat-embracing-the-chaos-2b4714e9</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "30 Days at NIAT – Embracing the Chaos" → "My First 30 Days at NIAT NSRIT: Embracing the Chaos"
 Meta title: "My First 30 Days at NIAT NSRIT: Embracing the Chaos"
@@ -3059,7 +3206,7 @@
 Body rewritten from the SEO report (340 → 461 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3069,23 +3216,23 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/72-hour-pursuit-challenge-team-collaboration-niat-nsrit</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Three Days That Changed How I Think: My 72-Hour Pursuit Challenge at NIAT" → "My 72-Hour Pursuit at NIAT NSRIT: Learning to Listen Under Pressure"
 Meta title: "72-Hour Pursuit at NIAT NSRIT: My Teamwork Experience"
@@ -3093,7 +3240,7 @@
 Body rewritten from the SEO report (597 → 723 words); H2 headings 5 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 73 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3102,23 +3249,23 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/a-complete-tour-of-the-niat-campus-vizag-7455c8a4</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "A Complete Tour of the NIAT Campus vizag" → "NIAT NSRIT Campus Life: The Places That Became Familiar to Me"
 Meta title: "NIAT NSRIT Campus Life: A Student’s Favourite Spots"
@@ -3126,7 +3273,7 @@
 Body rewritten from the SEO report (457 → 632 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3136,23 +3283,23 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/a-day-in-the-life-of-an-niat-x-nsrit-student-what-actually-happens-hour-by-hour-38d1b5b5</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "A Day in the Life of an NIAT x NSRIT Student — What Actually Happens Hour by Hour" → "A Day at NIAT NSRIT: Classes, Clubs and Hostel Life, Hour by Hour"
 Meta title: "A Day at NIAT NSRIT: A Student’s Hour-by-Hour Account"
@@ -3160,7 +3307,7 @@
 Body rewritten from the SEO report (2389 → 2483 words); H2 headings 0 → 13; FAQ section added</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 81 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3170,23 +3317,23 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/advanced-technology-club-real-robotics-automation-projects-niat-nsrit</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How the Advanced Technology Club at NIAT Taught Me Real Robotics Beyond the Classroom" → "Inside NIAT NSRIT’s Advanced Technology Club: My Robotics Experience"
 Meta title: "NIAT NSRIT Advanced Technology Club: Robotics &amp; Projects"
@@ -3194,7 +3341,7 @@
 Body rewritten from the SEO report (790 → 934 words); H2 headings 5 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 85 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3203,23 +3350,23 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/beachside-conversations-that-became-memories-a4129ea4</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Beachside Conversations That Became Memories" → "Beachside Conversations in Vizag: The College Memories I Keep"
 Meta title: "Beachside Conversations in Vizag: A Student’s Memories"
@@ -3227,7 +3374,7 @@
 Body rewritten from the SEO report (581 → 434 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 64 characters (over 60)
@@ -3237,23 +3384,23 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/campus-clubs-media-club-accident-niat-nsrit-visakhapatnam</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Walking Into Campus Clubs by Accident: How NIAT's Media Club Changed My View of College Life" → "Finding NIAT NSRIT’s Media Club by Accident: An Evening That Stayed With Me"
 Meta title: "Finding NIAT NSRIT’s Media Club by Accident"
@@ -3261,7 +3408,7 @@
 Body rewritten from the SEO report (406 → 544 words); H2 headings 3 → 4; FAQ section added</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 92 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3270,23 +3417,23 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/career-wins-celebrating-growth-success-and-achievement-f168371e</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Career &amp; Wins – Celebrating Growth, Success, and Achievement" → "My NIAT NSRIT Wins: A Chess Title and Gen AI Club Responsibility"
 Meta title: "My NIAT NSRIT Wins: Chess and Gen AI Club Leadership"
@@ -3294,7 +3441,7 @@
 Body rewritten from the SEO report (315 → 415 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3304,23 +3451,23 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/chaos-to-belonging-first-30-days-niat-nsrit-visakhapatnam</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "From Chaos to Belonging: My First 30 Days at NIAT Transformed Everything" → "My First 30 Days at NIAT NSRIT: From Confusion to My First Python Win"
 Meta title: "First 30 Days at NIAT NSRIT: My First Python Win"
@@ -3328,7 +3475,7 @@
 Body rewritten from the SEO report (584 → 719 words); H2 headings 4 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 72 characters, cut off in search results
 Meta title was 67 characters (over 60)
@@ -3337,23 +3484,23 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/cultural-club-changed-college-experience-beyond-coding-niat-nsrit</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why NIAT's Cultural Club Changed My Entire College Experience Beyond Coding" → "My NIAT NSRIT Cultural Club Experience: Finding Space Beyond Coding"
 Meta title: "NIAT NSRIT Cultural Club: My Experience Beyond Coding"
@@ -3361,7 +3508,7 @@
 Body rewritten from the SEO report (412 → 559 words); H2 headings 3 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 75 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3370,23 +3517,23 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/every-achievement-has-a-story-my-journey-through-growth-challenges-and-wins-at-niat-cf2714c1</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Every Achievement Has a Story: My Journey Through Growth, Challenges, and Wins at NIAT" → "Small Wins at NIAT: How My Idea of Achievement Changed"
 Meta title: "Small Wins at NIAT: My Journey of Growth"
@@ -3394,7 +3541,7 @@
 Body rewritten from the SEO report (700 → 802 words); H2 headings 0 → 9; FAQ section added</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 86 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3404,23 +3551,23 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/exploring-nature-near-vizag-99367130</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Exploring Nature Near Vizag" → "Exploring Nature Near Vizag: What I Found Beyond the Coast"
 Meta title: "Exploring Nature Near Vizag: A Student’s Reflection"
@@ -3428,7 +3575,7 @@
 Body rewritten from the SEO report (546 → 407 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3438,23 +3585,23 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/exploring-visakhapatnam-as-an-nsrit-student-creating-memories-beyond-the-classroom-7c1c8bd7</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Exploring Visakhapatnam as an NSRIT Student: Creating Memories Beyond the Classroom" → "Exploring Visakhapatnam as an NSRIT Student: Outings, Food and Friends"
 Meta title: "Exploring Visakhapatnam as an NSRIT Student"
@@ -3462,7 +3609,7 @@
 Body rewritten from the SEO report (512 → 634 words); H2 headings 7 → 8; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 83 characters, cut off in search results
 Meta title was 70 characters (over 60)
@@ -3471,23 +3618,23 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/exploring-vizag-beyond-the-beaches-208c3a60</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Exploring Vizag Beyond the Beaches" → "Vizag Beyond the Beaches: A Student’s Look at Hills, History and Parks"
 Meta title: "Vizag Beyond the Beaches: A Student’s Perspective"
@@ -3495,7 +3642,7 @@
 Body rewritten from the SEO report (586 → 440 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3505,23 +3652,23 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/four-unexpected-campus-hangout-spots-niat-nsrit-visakhapatnam</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Four Unexpected Campus Spots That Actually Define College Life at NIAT" → "Four NIAT NSRIT Campus Hangouts That Shaped My College Life"
 Meta title: "Four NIAT NSRIT Campus Hangouts: A Student’s Story"
@@ -3529,7 +3676,7 @@
 Body rewritten from the SEO report (615 → 690 words); H2 headings 4 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 70 characters, cut off in search results
 Meta title was 73 characters (over 60)
@@ -3538,23 +3685,23 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/gesture-control-workshop-niat-visakhapatnam-student-experience</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Gesture Control Workshop @ NIAT – A Volunteer’s Story" → "Volunteering at NIAT’s Gesture-Control Workshop: ESP32, LEDs and Chaos"
 Meta title: "NIAT Gesture-Control Workshop: An ESP32 Volunteer Story"
@@ -3562,7 +3709,7 @@
 Body formatting fixed, text kept (482 → 461 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3572,23 +3719,23 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/how-accountability-accelerates-personal-growth-and-professional-excellence-b47f14ff</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How Accountability Helps NIAT Students Achieve True Success" → "Accountability for Students: Taking Ownership of Goals and Mistakes"
 Meta title: "Accountability for Students: Goals, Mistakes and Growth"
@@ -3596,7 +3743,7 @@
 Body rewritten from the SEO report (549 → 430 words); H2 headings 3 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 69 characters (over 60)
@@ -3605,23 +3752,23 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/how-niat-encourages-personal-growth-a0f66158</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How NIAT Encourages Personal Growth" → "Personal Growth at NIAT: What Responsibility and Setbacks Taught Me"
 Meta title: "Personal Growth at NIAT: Responsibility and Resilience"
@@ -3629,7 +3776,7 @@
 Body rewritten from the SEO report (741 → 497 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 61 characters (over 60)
@@ -3639,23 +3786,23 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/how-optimism-helps-you-overcome-challenges-and-achieve-goals-02125231</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Top Student Tips: How Optimism Helps NIAT Students Achieve Goals" → "Realistic Optimism for Students: Facing Challenges and Finding a Next Step"
 Meta title: "Realistic Optimism for Students Facing Challenges"
@@ -3663,7 +3810,7 @@
 Body rewritten from the SEO report (443 → 404 words); H2 headings 2 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 64 characters, cut off in search results
 Meta title was 72 characters (over 60)
@@ -3672,23 +3819,23 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/inter-campus-sports-collaboration-cricket-kabaddi-volleyball-niat-nsrit-visakhapatnam</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How Two B.Tech Campuses Built the Ultimate Sports Day: Cricket, Kabaddi, Volleyball &amp; Real Competition (NIAT NSRIT)" → "Organizing NIAT NSRIT Sports Day: Cricket, Kabaddi, Volleyball and Dodgeball"
 Meta title: "NIAT NSRIT Sports Day: An Organizer’s Experience"
@@ -3696,7 +3843,7 @@
 Body rewritten from the SEO report (449 → 602 words); H2 headings 4 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 115 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3705,23 +3852,23 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/learning-ai-at-niat-opportunities-and-challenges-e91f1c24</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Learning AI at NIAT: Opportunities and Challenges" → "Learning AI at NIAT: Practical Opportunities and Beginner Challenges"
 Meta title: "Learning AI at NIAT: Opportunities and Challenges"
@@ -3729,7 +3876,7 @@
 Body rewritten from the SEO report (585 → 420 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3739,23 +3886,23 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/my-favorite-sunset-spot-in-vizag-36363b42</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "My Favorite Sunset Spot in Vizag" → "Kailasagiri at Sunset: My Favourite Evening View in Vizag"
 Meta title: "Kailasagiri at Sunset: My Favourite Vizag View"
@@ -3763,7 +3910,7 @@
 Body rewritten from the SEO report (623 → 431 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 65 characters (over 60)
@@ -3773,23 +3920,23 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/niat-student-teaching-experience-zph-school-andhapuram</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "NIAT Teaching Program @ ZPH High School, Andhapuram – A Day as “Sir” 😄" → "Teaching at ZPH High School, Andhapuram: My Day as “Anna”"
 Meta title: "NIAT Teaching Visit to ZPH High School, Andhapuram"
@@ -3797,7 +3944,7 @@
 Body formatting fixed, text kept (475 → 469 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 70 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -3807,23 +3954,23 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/one-robotics-workshop-at-niat-changed-how-i-see-the-entire-field-be62c949</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "My First Year Student Experience in a NIAT Robotics Workshop" → "My NIAT Robotics Workshop: Learning a Robotic Arm Through Simulation"
 Meta title: "NIAT Robotics Workshop: My Robotic-Arm Simulation"
@@ -3831,7 +3978,7 @@
 Body rewritten from the SEO report (554 → 454 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 67 characters (over 60)
@@ -3841,23 +3988,79 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/rushikonda-beach-the-stress-buster-of-nsrit-students-4b1a9c71</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Body formatting fixed, text kept (396 → 394 words)</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Body was 396 words, under the 450 floor (every article under 450 failed the text-to-HTML audit)
+Formatting fixes only: typed '--' dashes, broken link, repeated opening lines, pasted chat-app styling</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/simhachalam-temple-the-pride-of-andhra-pradesh-9ba8cb5f</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Body formatting fixed, text kept (945 → 941 words); H2 headings 0 → 11</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>No H2 headings, so no structure for readers or search engines
+Formatting fixes only: typed '--' dashes, broken link, repeated opening lines, pasted chat-app styling</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Survival &amp; Food Fest – A Recipe for Memories" → "NIAT NSRIT Survival &amp; Food Fest: Stalls, Teamwork and Shared Memories"
 Meta title: "NIAT NSRIT Survival &amp; Food Fest: Stalls and Teamwork"
@@ -3865,7 +4068,7 @@
 Body rewritten from the SEO report (298 → 364 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 61 characters (over 60)
@@ -3875,23 +4078,23 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-best-places-to-relax-between-classes-544dd55d</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Best Places to Relax Between Classes" → "Where I Relax Between Classes at NIAT NSRIT"
 Meta title: "Where I Relax Between Classes at NIAT NSRIT"
@@ -3899,7 +4102,7 @@
 Body rewritten from the SEO report (450 → 601 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3909,23 +4112,23 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-campus-greenery-e58dbb15</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Campus Greenery" → "NIAT NSRIT Campus Greenery: My Break From Screens in Sontyam"
 Meta title: "NIAT NSRIT Campus Greenery: A Student’s Screen Break"
@@ -3933,7 +4136,7 @@
 Body rewritten from the SEO report (281 → 377 words); H2 headings 0 → 4; FAQ section added</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -3943,23 +4146,23 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-power-of-a-positive-learning-environment-9c9b0acd</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Power of a Positive Learning Environment" → "A Positive Learning Environment at NIAT: Why Support Mattered to Me"
 Meta title: "NIAT Learning Environment: Support and Shared Growth"
@@ -3967,7 +4170,7 @@
 Body rewritten from the SEO report (750 → 460 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 71 characters (over 60)
@@ -3977,23 +4180,23 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-real-value-of-hostel-life-isnt-the-roomits-the-people-9631a68e</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Real Value of Hostel Life Isn’t the Room—It’s the People" → "Hostel Life at NIAT: Why the People Mattered More Than the Room"
 Meta title: "Hostel Life at NIAT: Friendships and Independence"
@@ -4001,7 +4204,7 @@
 Body rewritten from the SEO report (558 → 622 words); H2 headings 0 → 9; FAQ section added</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -4011,23 +4214,23 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-stress-fun-and-growth-happening-all-at-once-098e6040</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Stress, Fun, and Growth Happening All at Once" → "NIAT NSRIT Student Life: Stress, Friendship and My Starlight 2025 Moment"
 Meta title: "NIAT NSRIT Student Life: Stress, Fun and Growth"
@@ -4035,7 +4238,7 @@
 Body rewritten from the SEO report (456 → 616 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 67 characters (over 60)
@@ -4045,23 +4248,23 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/thirty-days-in-what-nobody-tells-you-about-starting-at-niat-0c225ee4</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Thirty Days In: What Nobody Tells You About Starting at NIAT" → "My First Month at NIAT: Lost Classrooms, Lab Friends and a First Presentation"
 Meta title: "My First Month at NIAT: Finding My Rhythm"
@@ -4069,7 +4272,7 @@
 Body rewritten from the SEO report (741 → 887 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 63 characters (over 60)
@@ -4079,23 +4282,23 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/what-happens-when-you-ask-students-to-see-color-differently-niats-collage-competition-21ddf410</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How a Simple Photo Contest Changed How Students See the World" → "NIAT’s Color Collage Competition: Learning to Tell Stories Through Colour"
 Meta title: "NIAT Color Collage Competition: Seeing Campus Anew"
@@ -4103,7 +4306,7 @@
 Body rewritten from the SEO report (524 → 579 words); H2 headings 5 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 61 characters, cut off in search results
 Meta title was 67 characters (over 60)
@@ -4112,23 +4315,23 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/what-makes-niat-x-nsrit-different-from-a-regular-engineering-college-81a524f6</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "What Makes NIAT x NSRIT Different From a Regular Engineering College" → "NIAT NSRIT Through a Student’s Eyes: Practical Learning and Trade-Offs"
 Meta title: "NIAT NSRIT Student Perspective: Strengths and Limits"
@@ -4136,7 +4339,7 @@
 Body rewritten from the SEO report (924 → 526 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 68 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -4146,23 +4349,51 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/what-niat-actually-taught-me-about-tech-ethics-and-why-it-stuck-754f63df</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Formatting fixed (text unchanged); H2 headings 0 → 5</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>No H2 headings, so no structure for readers or search engines
+Formatting fixes only: typed '--' dashes, broken link, repeated opening lines, pasted chat-app styling</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/what-seniors-at-niat-x-nsrit-actually-do-for-first-year-students-95da7f46</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "What Seniors at NIAT x NSRIT Actually Do for First-Year Students" → "How Seniors Help First-Year Students at NIAT NSRIT"
 Meta title: "How Seniors Help First-Year Students at NIAT NSRIT"
@@ -4170,7 +4401,7 @@
 Body rewritten from the SEO report (810 → 877 words); H2 headings 0 → 5; FAQ section added</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 64 characters, cut off in search results
 Meta title was 68 characters (over 60)
@@ -4180,23 +4411,23 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-adaptability-is-the-secret-weapon-of-future-ready-leaders-b1a3e295</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Adaptability Is the Secret Weapon of Future-Ready Leaders" → "Adaptability at NIAT: What My AI Project and BRAVE Negotiations Taught Me"
 Meta title: "Adaptability: Lessons From My NIAT Projects"
@@ -4204,7 +4435,7 @@
 Body rewritten from the SEO report (1022 → 519 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 61 characters, cut off in search results
 Meta title was 71 characters (over 60)
@@ -4214,23 +4445,23 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-character-matters-more-than-talent-in-long-term-success-593e92b1</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Character Matters More Than Talent in Long-Term Success" → "Why Character Matters Alongside Talent: Lessons From My NIAT Journey"
 Meta title: "Character and Talent: Lessons From a NIAT Student"
@@ -4238,7 +4469,7 @@
 Body rewritten from the SEO report (976 → 493 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 65 characters (over 60)
@@ -4248,23 +4479,23 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-clubs-are-more-than-just-activities-e270c2a9</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Clubs Are More Than Just Activities" → "What NIAT Clubs Taught Me About Responsibility and Belonging"
 Meta title: "NIAT Student Clubs: Responsibility and Belonging"
@@ -4272,7 +4503,7 @@
 Body rewritten from the SEO report (800 → 510 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -4282,23 +4513,23 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-every-student-should-join-at-least-one-club-11682d4e</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Every Student Should Join at Least One Club" → "Why Joining a College Club Can Be Worth Your Time"
 Meta title: "Why Join a College Club? Skills, Friends and Balance"
@@ -4306,7 +4537,7 @@
 Body rewritten from the SEO report (577 → 688 words); H2 headings 0 → 8; FAQ section added</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 61 characters (over 60)
@@ -4316,23 +4547,23 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-humility-is-a-strength-not-a-weakness-in-leadership-and-life-d40f0324</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Humility Is a Strength, Not a Weakness, in Leadership and Life" → "Humility in Student Leadership: What Learning and Feedback Taught Me"
 Meta title: "Humility in Leadership: A NIAT Student’s Lessons"
@@ -4340,7 +4571,7 @@
 Body rewritten from the SEO report (1031 → 489 words); H2 headings 0 → 6; FAQ section added</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 66 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -4350,23 +4581,23 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-local-hangout-spots-become-part-of-your-college-story-947905a4</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Local Hangout Spots Become Part of Your College Story" → "Why Local Hangout Spots Became Part of My NIAT College Story"
 Meta title: "Local Hangout Spots and My NIAT College Story"
@@ -4374,7 +4605,7 @@
 Body rewritten from the SEO report (501 → 600 words); H2 headings 0 → 9; FAQ section added</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -4384,23 +4615,23 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-projects-matter-more-than-marks-41670106</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Projects Matter More Than Marks" → "Projects and Marks at NIAT: Why Building Gave My Learning Meaning"
 Meta title: "Projects and Marks: A NIAT Student’s Perspective"
@@ -4408,7 +4639,7 @@
 Body rewritten from the SEO report (799 → 516 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 71 characters (over 60)
@@ -4418,23 +4649,23 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-the-cafeteria-is-the-most-social-place-on-campus-c74e311f</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why the Cafeteria Is the Most Social Place on Campus" → "Why the NIAT Cafeteria Became My Favourite Place to Connect"
 Meta title: "NIAT Cafeteria Life: Friends, Food and Conversations"
@@ -4442,7 +4673,7 @@
 Body rewritten from the SEO report (488 → 576 words); H2 headings 0 → 9; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was 74 characters (over 60)
@@ -4452,23 +4683,23 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-the-gen-ai-club-inspires-students-to-stay-curious-082d373d</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why the Gen AI Club Inspires Students to Stay Curious" → "Why NIAT’s Gen AI Club Keeps Me Curious About Technology"
 Meta title: "NIAT Gen AI Club: Curiosity and Learning Together"
@@ -4476,7 +4707,7 @@
 Body rewritten from the SEO report (530 → 621 words); H2 headings 0 → 9; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -4486,23 +4717,23 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-the-transport-facility-makes-student-life-smoother-than-you-realize-category-amenities-8403ebdc</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why the Transport Facility Makes Student Life Smoother Than You Realize Category: Amenities" → "NIAT Transport and Student Life: Why a Dependable Commute Matters to Me"
 Meta title: "NIAT Transport: A Student’s View of the Daily Commute"
@@ -4510,7 +4741,7 @@
 Body rewritten from the SEO report (513 → 577 words); H2 headings 0 → 9; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 91 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -4520,411 +4751,551 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/industry-5-0-tech-labs-nsrit-niat-campus</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 184 words</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/media-club-color-collage-competition-nsrit-visakhapatnam</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/article/what-happens-when-you-ask-students-to-see-color-differently-niats-collage-competition-21ddf410
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 287 words</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/one-day-your-parents-will-ask-less-questions-4c9c31f2</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 115 words</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-7935e474</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Already unpublished; 301 now goes straight to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb (was a two-hop chain for the onboarding copies)
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate record: the same Food Fest body under another URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-e2a3443b</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Already unpublished; 301 now goes straight to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb (was a two-hop chain for the onboarding copies)
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate record: the same Food Fest body under another URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-where-creativity-meets-competition-1511df42</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C138" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 303 words</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-dark-reality-of-potential-8b8737d4</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 86 words</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-dark-truth-about-attention-9147ba87</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C140" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 87 words</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-first-step-into-niat-239f9219</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 114 words</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-friend-who-became-family-fbb35502</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 97 words</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-friend-who-corrected-you-instead-of-praising-you-4def1b13</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 96 words</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-friend-who-never-competed-with-you-99338489</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 83 words</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-onboarding-kit-the-first-step-into-the-niat-journey-0bebc7e2</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 297 words</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/the-onboarding-kit-the-first-step-into-the-niat-journey-21e1e56e</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Already unpublished; 301 now goes straight to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb (was a two-hop chain for the onboarding copies)
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate record: the same Food Fest body under another URL with a 'Welcome Kit for Freshers' title the page could not deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/the-onboarding-kit-the-first-step-into-the-niat-journey-c0522fe8</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Already unpublished; 301 now goes straight to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb (was a two-hop chain for the onboarding copies)
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate record: the same Food Fest body under another URL with a 'Welcome Kit for Freshers' title the page could not deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-nsrit/article/the-onboarding-kit-the-first-step-into-the-niat-journey-fa0df14f</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Redirect (301)</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Already unpublished; 301 now goes straight to https://www.niatinsider.com/niat-nsrit/article/survival-food-fest-a-recipe-for-memories-72b428eb (was a two-hop chain for the onboarding copies)
+Removed from sitemap</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate record: the same Food Fest body under another URL with a 'Welcome Kit for Freshers' title the page could not deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/the-parent-who-never-said-they-were-tired-313d576e</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 109 words</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>Nadimpalli Satyanarayana Raju Institute of Technology</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-nsrit/article/why-the-transport-facility-makes-student-life-more-comfortable-42d4449c</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-nsrit/article/why-the-transport-facility-makes-student-life-smoother-than-you-realize-category-amenities-8403ebdc
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E137" s="3" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 305 words</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University  (25 articles)</t>
         </is>
       </c>
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
-      <c r="D138" s="3" t="n"/>
-      <c r="E138" s="3" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="B151" s="3" t="n"/>
+      <c r="C151" s="3" t="n"/>
+      <c r="D151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/30-days-content-creator-niat-campus-life-sgu-hostel-reality</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "My First 30 Days as a Content Creator in NIAT Campus Life (Sanjay Ghodawat University)" → "Hostel Life Is Not Instagram: My First 30 Days Filming NIAT"
 Meta title: "Hostel Life Is Not Instagram: 30 Days at NIAT Kolhapur"
@@ -4933,7 +5304,7 @@
 Body rewritten from the SEO report (515 → 630 words); H2 headings 5 → 6</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 86 characters, cut off in search results
 Meta title was 71 characters (over 60)
@@ -4943,23 +5314,23 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/building-ai-projects-beats-theory-genai-masterclass-niat-sgu</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Building AI Projects Beats Theory Every Time (GenAI Masterclass at NIAT SGU)" → "Why Building AI Projects Beats Theory Every Time"
 Meta title: "GenAI Masterclass at NIAT Kolhapur: Projects Over Theory"
@@ -4968,7 +5339,7 @@
 Body formatting fixed, text kept (351 → 351 words)</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 80 characters, cut off in search results
 Meta title was 95 characters (over 60)
@@ -4979,23 +5350,23 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/first-year-btech-ai-python-real-skills-niat-sgu</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "What My First B.Tech Year Actually Taught Me About AI &amp; Python (NIAT SGU)" → "What My First B.Tech Year Taught Me About AI and Python"
 Meta title: "First-Year AI and Python at NIAT Kolhapur (SGU)"
@@ -5004,7 +5375,7 @@
 Body formatting fixed, text kept (479 → 479 words)</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 73 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5014,23 +5385,23 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/first-year-niat-sgu-kolhapur-honest-student-review</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "My first-year Honest Experience" → "My First Year at NIAT SGU: An Honest Experience"
 Meta title: "My First Year at NIAT Kolhapur: An Honest Experience"
@@ -5038,7 +5409,7 @@
 Keywords: 8 → 4 focused terms</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -5046,23 +5417,23 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/funniest-question-project-presentation-story</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "The Funniest Question I Was Asked During a Project Presentation 😂" → "The Funniest Question I Was Asked During a Project Presentation"
 Meta title: "The Funniest Question a Judge Asked Me at NIAT Kolhapur"
@@ -5070,7 +5441,7 @@
 Keywords: 8 → 4 focused terms</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 65 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5078,23 +5449,23 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/nervous-first-day-student-nsgc-president-niat-sgu</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How I Went from Nervous First-Day Student to NSGC President at NIAT SGU" → "From Nervous First-Day Student to NSGC President"
 Meta title: "From Nervous First-Day Student to NSGC President at NIAT"
@@ -5103,7 +5474,7 @@
 Body formatting fixed, text kept (783 → 787 words)</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 71 characters, cut off in search results
 Meta title was 75 characters (over 60)
@@ -5113,23 +5484,23 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-clubs-student-life-activities-campus</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Clubs &amp; Student Life at NIAT" → "Clubs and Student Life at NIAT Kolhapur"
 Meta title: "NIAT Kolhapur Clubs: 7 Groups, Monthly Events"
@@ -5138,7 +5509,7 @@
 Body rewritten from the SEO report (173 → 720 words); H2 headings 0 → 4; FAQ section added; extra H1 in body removed</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -5148,23 +5519,23 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-kolhapur-campus-sahyadri-hills-student-review</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "NIAT Kolhapur — Where the Sahyadri Hills Cradle a Campus" → "NIAT Kolhapur: 165 Acres in the Sahyadri Hills"
 Meta title: "NIAT Kolhapur Campus: 165 Acres in the Sahyadri Hills"
@@ -5173,7 +5544,7 @@
 Body rewritten from the SEO report (512 → 751 words); H2 headings 0 → 7; FAQ section added</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Old H1 was vague or did not say what the page is about
 Meta title was generic / repeated the H1
@@ -5183,23 +5554,23 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-day-campus-experience</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Meta title: "My First Day at NIAT Kolhapur: A Dead Phone at 2pm"
 Meta description rewritten with the article's own specifics
@@ -5207,7 +5578,7 @@
 Body formatting fixed, text kept (719 → 719 words)</t>
         </is>
       </c>
-      <c r="E147" s="3" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5216,23 +5587,23 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-day-campus-life</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Meta title: "My First Day at NIAT Kolhapur (SGU): Poha and A Block"
 Meta description rewritten with the article's own specifics
@@ -5240,7 +5611,7 @@
 Body formatting fixed, text kept (839 → 839 words)</t>
         </is>
       </c>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5249,23 +5620,23 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-week-btech-life</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Meta title: "Poha at 6:50am: The Real First Month at NIAT Kolhapur"
 Meta description rewritten with the article's own specifics
@@ -5273,7 +5644,7 @@
 Body formatting fixed, text kept (1000 → 1000 words)</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5282,23 +5653,23 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-week-campus-life</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Meta title: "Lost on a Campus This Big: My First Week at NIAT SGU"
 Meta description rewritten with the article's own specifics
@@ -5306,7 +5677,7 @@
 Body formatting fixed, text kept (764 → 764 words)</t>
         </is>
       </c>
-      <c r="E150" s="3" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>Meta title was 63 characters (over 60)
 Meta description was generic, no specifics from the article
@@ -5315,23 +5686,23 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-week-exam-campus-life</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Meta title: "Exams, Rain and Terrible Tea: My First Week at NIAT"
 Meta description rewritten with the article's own specifics
@@ -5339,7 +5710,7 @@
 Body formatting fixed, text kept (997 → 997 words)</t>
         </is>
       </c>
-      <c r="E151" s="3" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5348,23 +5719,23 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-year-daily-life-honest</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Meta title: "A Day at NIAT Kolhapur: Mess, Classes, a Long Walk"
 Meta description rewritten with the article's own specifics
@@ -5372,7 +5743,7 @@
 Body formatting fixed, text kept (920 → 920 words)</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5381,23 +5752,23 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-first-year-practical-skills-honest-review</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Meta title: "First-Year Classes at NIAT Kolhapur: Real Skills Only"
 Meta description rewritten with the article's own specifics
@@ -5405,7 +5776,7 @@
 Body formatting fixed, text kept (927 → 927 words)</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5414,23 +5785,23 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-student-stall-entrepreneurship-club-experience</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Meta title: "Running a Stall at NIAT Kolhapur: What Actually Sold"
 Meta description rewritten with the article's own specifics
@@ -5438,7 +5809,7 @@
 Body rewritten from the SEO report (1032 → 1243 words); H2 headings 6 → 7</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>Meta title was generic / repeated the H1
 Meta description was generic, no specifics from the article
@@ -5447,23 +5818,23 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/virtual-robotic-arm-workshop-control-systems-simulation-niat-sgu</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How a Virtual Robotic Arm Workshop Changed My Understanding of Control Systems (NIAT SGU)" → "How a Virtual Robotic Arm Changed How I See Control Systems"
 Meta title: "Virtual Robotic Arm Workshop at NIAT Kolhapur (SGU)"
@@ -5472,7 +5843,7 @@
 Body rewritten from the SEO report (446 → 559 words); H2 headings 4 → 5</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 89 characters, cut off in search results
 Meta title was 66 characters (over 60)
@@ -5482,266 +5853,266 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/art-swap-collaborative-event-sgu-kolhapur-clubs</t>
         </is>
       </c>
-      <c r="C156" s="7" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-clubs-student-life-activities-campus
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 288 words</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/career-success-mindset-not-luck-niat-students</t>
         </is>
       </c>
-      <c r="C157" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/articles
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E157" s="3" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>Removed from the site because it is too short to publish. Expand it with your own experience (specific names, places, numbers or events) and resubmit.
 Only 154 words</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/first-30-days-at-niat-real-student-experience</t>
         </is>
       </c>
-      <c r="C158" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/30-days-content-creator-niat-campus-life-sgu-hostel-reality
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 314 words</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/my-first-30-days-at-niat-real-student-experience</t>
         </is>
       </c>
-      <c r="C159" s="7" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/30-days-content-creator-niat-campus-life-sgu-hostel-reality
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E159" s="3" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 314 words</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sgu-campus-life-green-peaceful-environment</t>
         </is>
       </c>
-      <c r="C160" s="7" t="inlineStr">
+      <c r="C173" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-kolhapur-campus-sahyadri-hills-student-review
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 274 words</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B174" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sgu-tech-workshops-learning-experience-review</t>
         </is>
       </c>
-      <c r="C161" s="7" t="inlineStr">
+      <c r="C174" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/virtual-robotic-arm-workshop-control-systems-simulation-niat-sgu
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E161" s="3" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 130 words</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/pitch-worst-idea-event-sgu-kolhapur-club-activity</t>
         </is>
       </c>
-      <c r="C162" s="7" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-clubs-student-life-activities-campus
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 286 words</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>Sanjay Ghodawat University</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/vr-stall-48-hour-challenge-niat-student-experience</t>
         </is>
       </c>
-      <c r="C163" s="7" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-sanjay-ghodawat-university/article/niat-sanjay-ghodawat-university-student-stall-entrepreneurship-club-experience
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 222 words</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Yenepoya University  (10 articles)</t>
         </is>
       </c>
-      <c r="B164" s="3" t="n"/>
-      <c r="C164" s="3" t="n"/>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/ai-tools-mentoring-niat-tech-club-student-experience</t>
         </is>
       </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How I Mentored Students on Cutting-Edge AI Tools at NIAT Tech Club" → "How I Mentored Students on AI Tools at NIAT Tech Club"
 Meta title: "Mentoring Students on AI Tools at NIAT Tech Club"
@@ -5750,7 +6121,7 @@
 Body formatting fixed, text kept (931 → 929 words); H2 headings 0 → 7</t>
         </is>
       </c>
-      <c r="E165" s="3" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 66 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5760,23 +6131,23 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/best-beaches-parks-near-niat-yenepoya-panambur-tannirbhavi-hangout-spots</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Best Beaches &amp; Parks Near NIAT Yenepoya: Panambur, Tannirbhavi &amp; Hidden Gems" → "Beaches and Parks Near NIAT Yenepoya: Panambur to Kadri"
 Meta title: "Beaches and Parks Near NIAT Yenepoya, With Bus Routes"
@@ -5785,7 +6156,7 @@
 Body rewritten from the SEO report (681 → 980 words); H2 headings 4 → 5</t>
         </is>
       </c>
-      <c r="E166" s="3" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 76 characters, cut off in search results
 Meta title was 75 characters (over 60)
@@ -5795,23 +6166,23 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/ethics-accountability-tech-culture-niat-yenepoya-university</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Why Ethics and Accountability Actually Matter in Tech - Real Stories from NIAT Yenepoya" → "Why Ethics and Accountability Actually Matter in Tech"
 Meta title: "Ethics and Accountability at NIAT Yenepoya: Real Stories"
@@ -5820,7 +6191,7 @@
 Body formatting fixed, text kept (622 → 622 words)</t>
         </is>
       </c>
-      <c r="E167" s="3" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 87 characters, cut off in search results
 Meta title was 69 characters (over 60)
@@ -5830,23 +6201,23 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/first-year-ai-app-1000-users-global-reach-hackmate</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "I Built an AI App in My First Year — and It Reached 1,000+ Users Across 10+ Countries in One Month" → "I Built an AI App in My First Year. It Reached 10 Countries."
 Meta title: "I Built an AI App in First Year: 1,000+ Users"
@@ -5855,7 +6226,7 @@
 Body formatting fixed, text kept (1416 → 1394 words); H2 headings 0 → 8</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 98 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5865,23 +6236,23 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/first-year-students-international-hackathon-top-ranking</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "Top 69 Out of 15,000+ Teams: How We Competed at an International Hackathon in Our First Year" → "Top 69 Out of 15,000+ Teams, in Our First Year"
 Meta title: "Top 69 of 15,000+: The GO-BRICS Energy-O-Thon"
@@ -5890,7 +6261,7 @@
 Body formatting fixed, text kept (1198 → 1173 words); H2 headings 0 → 8</t>
         </is>
       </c>
-      <c r="E169" s="3" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 92 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5900,23 +6271,23 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/first-year-students-win-national-hackathon-fourth-place</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "4th Place at a National Hackathon in Our First Year: Our Hackwise 2.0 Story" → "4th Place at a National Hackathon in Our First Year"
 Meta title: "4th at Hackwise 2.0: A First-Year Hackathon Story"
@@ -5925,7 +6296,7 @@
 Body rewritten from the SEO report (1248 → 1222 words); H2 headings 0 → 8</t>
         </is>
       </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 75 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5935,23 +6306,23 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/niat-business-challenge-winning-team-5000-revenue</t>
         </is>
       </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "How We Made ₹5,000 in a Day and Won Best Marketing Team at the NIAT Business Challenge" → "How We Made ₹5,000 in a Day and Won Best Marketing Team"
 Meta title: "How We Made ₹5,000 in a Day at NIAT Yenepoya"
@@ -5960,7 +6331,7 @@
 Body rewritten from the SEO report (1402 → 1374 words); H2 headings 0 → 8</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 86 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -5970,23 +6341,23 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/student-media-head-openloop-hackathon-yenepoya-mangalore</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "From Applicant to Media &amp; Graphics Head: How I Helped Bring OPENLOOP to Life" → "From Applicant to Media Head: Bringing OPENLOOP to Life"
 Meta title: "Media Head for OPENLOOP: A NIAT Yenepoya Story"
@@ -5995,7 +6366,7 @@
 Body rewritten from the SEO report (1121 → 1052 words); H2 headings 1 → 7</t>
         </is>
       </c>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 76 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -6004,23 +6375,23 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/yenepoya-students-openai-buildathon-top-74-global</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>H1 changed: "From 75,000+ Participants to Top 74: Our Journey at the OpenAI Buildathon 2026" → "From 75,000 Participants to Top 74: Our Buildathon Story"
 Meta title: "Top 74 of 75,000: Our OpenAI Buildathon 2026 Story"
@@ -6029,7 +6400,7 @@
 Body rewritten from the SEO report (1387 → 1319 words); H2 headings 1 → 9</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Old H1 was 78 characters, cut off in search results
 Meta title was generic / repeated the H1
@@ -6038,51 +6409,573 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>Yenepoya University</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>https://www.niatinsider.com/niat-yenepoya-university/article/weekend-escapes-tannir-bhavi-beach-kadri-park-mental-health-reset-niat-yenepoya</t>
         </is>
       </c>
-      <c r="C174" s="7" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Unpublished and 301-redirected to https://www.niatinsider.com/niat-yenepoya-university/article/best-beaches-parks-near-niat-yenepoya-panambur-tannirbhavi-hangout-spots
 Removed from sitemap</t>
         </is>
       </c>
-      <c r="E174" s="3" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Merged: another article on this campus covers the same topic, so this one has been removed and now points to it.
 Only 392 words</t>
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University  (5 articles)</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n"/>
+      <c r="C188" s="3" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-ajeenkya-dy-patil-university/article/chaotic-btech-mornings-chia-seeds-earring-decisions-campus-life-niat-pune</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 6 H2 sections and 846 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-ajeenkya-dy-patil-university/article/niat-ajeenkya-dy-patil-buildathon-experience</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 761 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-ajeenkya-dy-patil-university/article/niat-ajeenkya-dy-patil-university-content-creation-workshop-100-post-theory</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 805 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-ajeenkya-dy-patil-university/article/niat-ajeenkya-dy-patil-university-first-year-honest-experience</t>
+        </is>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 6 H2 sections and 930 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-ajeenkya-dy-patil-university/article/niat-college-life-honest-review-curriculum-faculty-placements-adypu-pune</t>
+        </is>
+      </c>
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 687 words, so it is good to go as written. Note: verify the placement statements before promoting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Noida International University  (11 articles)</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n"/>
+      <c r="C194" s="3" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-clubs-community-first-year</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 910 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-college-fest-experience-first-year</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 930 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-exam-study-mistake-first-year</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 963 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-buildathon-experience</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 747 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-semester-honest-experience</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 6 H2 sections and 1032 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-week-btech-experience</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 6 H2 sections and 906 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-year-btech-honest-review</t>
+        </is>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 859 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-year-experience-review</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 8 H2 sections and 1314 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-year-projects-inspire</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 800 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-first-year-survive-music-motivation</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 4 H2 sections and 893 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-noida-international-university/article/niat-noida-international-university-workshop-film-competition-busy-day</t>
+        </is>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 5 H2 sections and 846 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Malla Reddy Vishwavidyapeeth  (2 articles)</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n"/>
+      <c r="C206" s="3" t="n"/>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Malla Reddy Vishwavidyapeeth</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-malla-reddy-vishwavidyapeeth/article/first-day-packing-checklist-essentials-niat-mrv</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 3 H2 sections and 393 words, so it is good to go as written. Note: 393 words is under the 450 floor; expand when the author can.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>Malla Reddy Vishwavidyapeeth</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>https://www.niatinsider.com/niat-malla-reddy-vishwavidyapeeth/article/skills-matter-more-than-cgpa-communication-coding-fundamentals-niat-mrv</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>Left as is</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Not changed</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Already in the site's article template (ni-article) with 3 H2 sections and 514 words, so it is good to go as written.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E174"/>
-  <mergeCells count="9">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A69:E69"/>
+  <autoFilter ref="A1:E208"/>
+  <mergeCells count="12">
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A138:E138"/>
-    <mergeCell ref="A164:E164"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A194:E194"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="A188:E188"/>
+    <mergeCell ref="A70:E70"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C70 C71 C72 C73 C74 C75 C76 C78 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C107 C108 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134 C135 C136 C137 C139 C140 C141 C142 C143 C144 C145 C146 C147 C148 C149 C150 C151 C152 C153 C154 C155 C156 C157 C158 C159 C160 C161 C162 C163 C165 C166 C167 C168 C169 C170 C171 C172 C173 C174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Published with changes,Published (noindex),Redirect (301),Removed"</formula1>
+    <dataValidation sqref="C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C71 C72 C73 C74 C75 C76 C77 C79 C80 C81 C82 C83 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C107 C108 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134 C135 C136 C137 C138 C139 C140 C141 C142 C143 C144 C145 C146 C147 C148 C149 C150 C152 C153 C154 C155 C156 C157 C158 C159 C160 C161 C162 C163 C164 C165 C166 C167 C168 C169 C170 C171 C172 C173 C174 C175 C176 C178 C179 C180 C181 C182 C183 C184 C185 C186 C187 C189 C190 C191 C192 C193 C195 C196 C197 C198 C199 C200 C201 C202 C203 C204 C205 C207 C208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Published with changes,Left as is,Published (noindex),Redirect (301),Removed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -6149,19 +7042,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId79"/>
@@ -6215,19 +7108,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId145"/>
@@ -6240,16 +7133,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6261,39 +7185,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Campus</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Published with changes</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Published with changes</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Published (noindex)</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Redirect (301)</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Removed</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -6318,6 +7242,9 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -6331,15 +7258,18 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>27</v>
       </c>
     </row>
@@ -6356,12 +7286,15 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6375,16 +7308,19 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>11</v>
+      <c r="G5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -6403,9 +7339,12 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6419,16 +7358,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="G7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6438,19 +7380,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>58</v>
+      <c r="G8" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -6466,12 +7411,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6488,35 +7436,116 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ajeenkya DY Patil University</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Noida International University</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Malla Reddy Vishwavidyapeeth</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>125</v>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="B14" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="E14" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>164</v>
+      <c r="G14" s="10" t="n">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
